--- a/data/00992A/20260427.xlsx
+++ b/data/00992A/20260427.xlsx
@@ -384,7 +384,7 @@
         <v>基金淨資產價值(元)</v>
       </c>
       <c r="B1" t="str">
-        <v>TWD 48,550,452,697</v>
+        <v>TWD 49,159,998,483</v>
       </c>
     </row>
     <row r="2">
@@ -392,7 +392,7 @@
         <v>每受益權單位淨資產價值(元)-台幣交易</v>
       </c>
       <c r="B2" t="str">
-        <v>TWD 16.9</v>
+        <v>TWD 16.88</v>
       </c>
     </row>
     <row r="3">
@@ -400,7 +400,7 @@
         <v>已發行受益權單位總數-台幣交易</v>
       </c>
       <c r="B3" t="str">
-        <v>2,872,455,000</v>
+        <v>2,912,455,000</v>
       </c>
     </row>
   </sheetData>
@@ -436,7 +436,7 @@
         <v>台積電</v>
       </c>
       <c r="C2" t="str">
-        <v>5.9%</v>
+        <v>6.04%</v>
       </c>
       <c r="D2" t="str">
         <v>1,311,000</v>
@@ -450,7 +450,7 @@
         <v>台光電</v>
       </c>
       <c r="C3" t="str">
-        <v>4.95%</v>
+        <v>5.17%</v>
       </c>
       <c r="D3" t="str">
         <v>537,000</v>
@@ -464,7 +464,7 @@
         <v>緯穎</v>
       </c>
       <c r="C4" t="str">
-        <v>4.44%</v>
+        <v>4.63%</v>
       </c>
       <c r="D4" t="str">
         <v>465,000</v>
@@ -472,30 +472,30 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>8996</v>
+        <v>3037</v>
       </c>
       <c r="B5" t="str">
-        <v>高力</v>
+        <v>欣興</v>
       </c>
       <c r="C5" t="str">
-        <v>3.91%</v>
+        <v>3.94%</v>
       </c>
       <c r="D5" t="str">
-        <v>1,689,000</v>
+        <v>2,310,000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>3105</v>
+        <v>8996</v>
       </c>
       <c r="B6" t="str">
-        <v>穩懋</v>
+        <v>高力</v>
       </c>
       <c r="C6" t="str">
-        <v>3.87%</v>
+        <v>3.68%</v>
       </c>
       <c r="D6" t="str">
-        <v>3,433,000</v>
+        <v>1,689,000</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         <v>貿聯-KY</v>
       </c>
       <c r="C7" t="str">
-        <v>3.8%</v>
+        <v>3.57%</v>
       </c>
       <c r="D7" t="str">
         <v>667,000</v>
@@ -514,30 +514,30 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>3037</v>
+        <v>3017</v>
       </c>
       <c r="B8" t="str">
-        <v>欣興</v>
+        <v>奇鋐</v>
       </c>
       <c r="C8" t="str">
-        <v>3.76%</v>
+        <v>3.47%</v>
       </c>
       <c r="D8" t="str">
-        <v>2,310,000</v>
+        <v>601,000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>3017</v>
+        <v>3105</v>
       </c>
       <c r="B9" t="str">
-        <v>奇鋐</v>
+        <v>穩懋</v>
       </c>
       <c r="C9" t="str">
-        <v>3.65%</v>
+        <v>3.44%</v>
       </c>
       <c r="D9" t="str">
-        <v>601,000</v>
+        <v>3,433,000</v>
       </c>
     </row>
     <row r="10">
@@ -548,7 +548,7 @@
         <v>智邦</v>
       </c>
       <c r="C10" t="str">
-        <v>3.16%</v>
+        <v>3.17%</v>
       </c>
       <c r="D10" t="str">
         <v>716,000</v>
@@ -562,7 +562,7 @@
         <v>精測</v>
       </c>
       <c r="C11" t="str">
-        <v>3.16%</v>
+        <v>3.06%</v>
       </c>
       <c r="D11" t="str">
         <v>422,000</v>
@@ -576,7 +576,7 @@
         <v>穎崴</v>
       </c>
       <c r="C12" t="str">
-        <v>3.13%</v>
+        <v>2.94%</v>
       </c>
       <c r="D12" t="str">
         <v>151,000</v>
@@ -584,30 +584,30 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>6442</v>
+        <v>6223</v>
       </c>
       <c r="B13" t="str">
-        <v>光聖</v>
+        <v>旺矽</v>
       </c>
       <c r="C13" t="str">
-        <v>3.04%</v>
+        <v>2.87%</v>
       </c>
       <c r="D13" t="str">
-        <v>785,000</v>
+        <v>289,000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>6223</v>
+        <v>6442</v>
       </c>
       <c r="B14" t="str">
-        <v>旺矽</v>
+        <v>光聖</v>
       </c>
       <c r="C14" t="str">
-        <v>2.77%</v>
+        <v>2.83%</v>
       </c>
       <c r="D14" t="str">
-        <v>289,000</v>
+        <v>785,000</v>
       </c>
     </row>
     <row r="15">
@@ -618,7 +618,7 @@
         <v>群聯</v>
       </c>
       <c r="C15" t="str">
-        <v>2.46%</v>
+        <v>2.65%</v>
       </c>
       <c r="D15" t="str">
         <v>711,000</v>
@@ -632,7 +632,7 @@
         <v>嘉澤</v>
       </c>
       <c r="C16" t="str">
-        <v>2.43%</v>
+        <v>2.58%</v>
       </c>
       <c r="D16" t="str">
         <v>468,000</v>
@@ -640,226 +640,226 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>3081</v>
+        <v>3443</v>
       </c>
       <c r="B17" t="str">
-        <v>聯亞</v>
+        <v>創意</v>
       </c>
       <c r="C17" t="str">
-        <v>2.21%</v>
+        <v>2.09%</v>
       </c>
       <c r="D17" t="str">
-        <v>380,000</v>
+        <v>260,000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>3163</v>
+        <v>7751</v>
       </c>
       <c r="B18" t="str">
-        <v>波若威</v>
+        <v>竑騰</v>
       </c>
       <c r="C18" t="str">
-        <v>2.2%</v>
+        <v>2.09%</v>
       </c>
       <c r="D18" t="str">
-        <v>924,000</v>
+        <v>388,000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>3653</v>
+        <v>2059</v>
       </c>
       <c r="B19" t="str">
-        <v>健策</v>
+        <v>川湖</v>
       </c>
       <c r="C19" t="str">
-        <v>2.18%</v>
+        <v>2.08%</v>
       </c>
       <c r="D19" t="str">
-        <v>197,000</v>
+        <v>258,000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>3443</v>
+        <v>8046</v>
       </c>
       <c r="B20" t="str">
-        <v>創意</v>
+        <v>南電</v>
       </c>
       <c r="C20" t="str">
-        <v>2.16%</v>
+        <v>2.06%</v>
       </c>
       <c r="D20" t="str">
-        <v>260,000</v>
+        <v>1,108,000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>6584</v>
+        <v>3653</v>
       </c>
       <c r="B21" t="str">
-        <v>南俊國際</v>
+        <v>健策</v>
       </c>
       <c r="C21" t="str">
-        <v>2.03%</v>
+        <v>1.99%</v>
       </c>
       <c r="D21" t="str">
-        <v>1,337,000</v>
+        <v>197,000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>2059</v>
+        <v>3081</v>
       </c>
       <c r="B22" t="str">
-        <v>川湖</v>
+        <v>聯亞</v>
       </c>
       <c r="C22" t="str">
-        <v>2.02%</v>
+        <v>1.96%</v>
       </c>
       <c r="D22" t="str">
-        <v>258,000</v>
+        <v>380,000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>8046</v>
+        <v>7769</v>
       </c>
       <c r="B23" t="str">
-        <v>南電</v>
+        <v>鴻勁</v>
       </c>
       <c r="C23" t="str">
-        <v>1.99%</v>
+        <v>1.96%</v>
       </c>
       <c r="D23" t="str">
-        <v>1,108,000</v>
+        <v>194,000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>2360</v>
+        <v>3163</v>
       </c>
       <c r="B24" t="str">
-        <v>致茂</v>
+        <v>波若威</v>
       </c>
       <c r="C24" t="str">
-        <v>1.93%</v>
+        <v>1.95%</v>
       </c>
       <c r="D24" t="str">
-        <v>487,000</v>
+        <v>924,000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>7751</v>
+        <v>2368</v>
       </c>
       <c r="B25" t="str">
-        <v>竑騰</v>
+        <v>金像電</v>
       </c>
       <c r="C25" t="str">
-        <v>1.92%</v>
+        <v>1.93%</v>
       </c>
       <c r="D25" t="str">
-        <v>388,000</v>
+        <v>669,000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>2368</v>
+        <v>2360</v>
       </c>
       <c r="B26" t="str">
-        <v>金像電</v>
+        <v>致茂</v>
       </c>
       <c r="C26" t="str">
-        <v>1.92%</v>
+        <v>1.91%</v>
       </c>
       <c r="D26" t="str">
-        <v>669,000</v>
+        <v>487,000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>7769</v>
+        <v>6584</v>
       </c>
       <c r="B27" t="str">
-        <v>鴻勁</v>
+        <v>南俊國際</v>
       </c>
       <c r="C27" t="str">
-        <v>1.89%</v>
+        <v>1.88%</v>
       </c>
       <c r="D27" t="str">
-        <v>194,000</v>
+        <v>1,337,000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>2308</v>
+        <v>2408</v>
       </c>
       <c r="B28" t="str">
-        <v>台達電</v>
+        <v>南亞科</v>
       </c>
       <c r="C28" t="str">
-        <v>1.53%</v>
+        <v>1.51%</v>
       </c>
       <c r="D28" t="str">
-        <v>357,000</v>
+        <v>3,280,000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>5274</v>
+        <v>2308</v>
       </c>
       <c r="B29" t="str">
-        <v>信驊</v>
+        <v>台達電</v>
       </c>
       <c r="C29" t="str">
-        <v>1.52%</v>
+        <v>1.47%</v>
       </c>
       <c r="D29" t="str">
-        <v>45,000</v>
+        <v>357,000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>3661</v>
+        <v>5274</v>
       </c>
       <c r="B30" t="str">
-        <v>世芯-KY</v>
+        <v>信驊</v>
       </c>
       <c r="C30" t="str">
-        <v>1.5%</v>
+        <v>1.46%</v>
       </c>
       <c r="D30" t="str">
-        <v>173,000</v>
+        <v>45,000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>4749</v>
+        <v>3661</v>
       </c>
       <c r="B31" t="str">
-        <v>新應材</v>
+        <v>世芯-KY</v>
       </c>
       <c r="C31" t="str">
-        <v>1.41%</v>
+        <v>1.46%</v>
       </c>
       <c r="D31" t="str">
-        <v>701,000</v>
+        <v>173,000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>2408</v>
+        <v>4749</v>
       </c>
       <c r="B32" t="str">
-        <v>南亞科</v>
+        <v>新應材</v>
       </c>
       <c r="C32" t="str">
-        <v>1.39%</v>
+        <v>1.38%</v>
       </c>
       <c r="D32" t="str">
-        <v>3,280,000</v>
+        <v>701,000</v>
       </c>
     </row>
     <row r="33">
@@ -870,7 +870,7 @@
         <v>台燿</v>
       </c>
       <c r="C33" t="str">
-        <v>1.37%</v>
+        <v>1.28%</v>
       </c>
       <c r="D33" t="str">
         <v>636,000</v>
@@ -878,58 +878,58 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>3529</v>
+        <v>6805</v>
       </c>
       <c r="B34" t="str">
-        <v>力旺</v>
+        <v>富世達</v>
       </c>
       <c r="C34" t="str">
         <v>1.25%</v>
       </c>
       <c r="D34" t="str">
-        <v>155,000</v>
+        <v>298,000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>6805</v>
+        <v>6531</v>
       </c>
       <c r="B35" t="str">
-        <v>富世達</v>
+        <v>愛普*</v>
       </c>
       <c r="C35" t="str">
-        <v>1.18%</v>
+        <v>1.08%</v>
       </c>
       <c r="D35" t="str">
-        <v>298,000</v>
+        <v>703,000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>6531</v>
+        <v>8358</v>
       </c>
       <c r="B36" t="str">
-        <v>愛普*</v>
+        <v>金居</v>
       </c>
       <c r="C36" t="str">
-        <v>1.14%</v>
+        <v>1.03%</v>
       </c>
       <c r="D36" t="str">
-        <v>703,000</v>
+        <v>1,508,000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>8358</v>
+        <v>6271</v>
       </c>
       <c r="B37" t="str">
-        <v>金居</v>
+        <v>同欣電</v>
       </c>
       <c r="C37" t="str">
-        <v>1.12%</v>
+        <v>0.92%</v>
       </c>
       <c r="D37" t="str">
-        <v>1,508,000</v>
+        <v>2,589,000</v>
       </c>
     </row>
     <row r="38">
@@ -940,7 +940,7 @@
         <v>弘塑</v>
       </c>
       <c r="C38" t="str">
-        <v>0.99%</v>
+        <v>0.9%</v>
       </c>
       <c r="D38" t="str">
         <v>154,000</v>
@@ -948,16 +948,16 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>6271</v>
+        <v>2454</v>
       </c>
       <c r="B39" t="str">
-        <v>同欣電</v>
+        <v>聯發科</v>
       </c>
       <c r="C39" t="str">
-        <v>0.95%</v>
+        <v>0.89%</v>
       </c>
       <c r="D39" t="str">
-        <v>2,589,000</v>
+        <v>180,000</v>
       </c>
     </row>
     <row r="40">
@@ -968,7 +968,7 @@
         <v>環宇-KY</v>
       </c>
       <c r="C40" t="str">
-        <v>0.85%</v>
+        <v>0.8%</v>
       </c>
       <c r="D40" t="str">
         <v>692,000</v>
@@ -982,7 +982,7 @@
         <v>尖點</v>
       </c>
       <c r="C41" t="str">
-        <v>0.61%</v>
+        <v>0.55%</v>
       </c>
       <c r="D41" t="str">
         <v>661,920</v>
@@ -996,7 +996,7 @@
         <v>景碩</v>
       </c>
       <c r="C42" t="str">
-        <v>0.53%</v>
+        <v>0.51%</v>
       </c>
       <c r="D42" t="str">
         <v>486,013</v>
@@ -1018,16 +1018,16 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>2454</v>
+        <v>2337</v>
       </c>
       <c r="B44" t="str">
-        <v>聯發科</v>
+        <v>旺宏</v>
       </c>
       <c r="C44" t="str">
-        <v>0.4%</v>
+        <v>0.37%</v>
       </c>
       <c r="D44" t="str">
-        <v>80,000</v>
+        <v>1,271,000</v>
       </c>
     </row>
     <row r="45">
@@ -1038,7 +1038,7 @@
         <v>雙鴻</v>
       </c>
       <c r="C45" t="str">
-        <v>0.38%</v>
+        <v>0.36%</v>
       </c>
       <c r="D45" t="str">
         <v>151,000</v>
@@ -1046,100 +1046,100 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>2337</v>
+        <v>3260</v>
       </c>
       <c r="B46" t="str">
-        <v>旺宏</v>
+        <v>威剛</v>
       </c>
       <c r="C46" t="str">
         <v>0.35%</v>
       </c>
       <c r="D46" t="str">
-        <v>1,271,000</v>
+        <v>393,000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>3711</v>
+        <v>5289</v>
       </c>
       <c r="B47" t="str">
-        <v>日月光投控</v>
+        <v>宜鼎</v>
       </c>
       <c r="C47" t="str">
-        <v>0.33%</v>
+        <v>0.34%</v>
       </c>
       <c r="D47" t="str">
-        <v>320,000</v>
+        <v>142,000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>3260</v>
+        <v>3711</v>
       </c>
       <c r="B48" t="str">
-        <v>威剛</v>
+        <v>日月光投控</v>
       </c>
       <c r="C48" t="str">
         <v>0.32%</v>
       </c>
       <c r="D48" t="str">
-        <v>393,000</v>
+        <v>320,000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>5289</v>
+        <v>3491</v>
       </c>
       <c r="B49" t="str">
-        <v>宜鼎</v>
+        <v>昇達科</v>
       </c>
       <c r="C49" t="str">
         <v>0.32%</v>
       </c>
       <c r="D49" t="str">
-        <v>142,000</v>
+        <v>97,000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>3491</v>
+        <v>2486</v>
       </c>
       <c r="B50" t="str">
-        <v>昇達科</v>
+        <v>一詮</v>
       </c>
       <c r="C50" t="str">
-        <v>0.31%</v>
+        <v>0.26%</v>
       </c>
       <c r="D50" t="str">
-        <v>97,000</v>
+        <v>567,000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>2486</v>
+        <v>2344</v>
       </c>
       <c r="B51" t="str">
-        <v>一詮</v>
+        <v>華邦電</v>
       </c>
       <c r="C51" t="str">
-        <v>0.26%</v>
+        <v>0.17%</v>
       </c>
       <c r="D51" t="str">
-        <v>567,000</v>
+        <v>893,000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>2344</v>
+        <v>3529</v>
       </c>
       <c r="B52" t="str">
-        <v>華邦電</v>
+        <v>力旺</v>
       </c>
       <c r="C52" t="str">
-        <v>0.16%</v>
+        <v>0.03%</v>
       </c>
       <c r="D52" t="str">
-        <v>893,000</v>
+        <v>4,000</v>
       </c>
     </row>
   </sheetData>
@@ -1158,7 +1158,7 @@
         <v>應收付證券款</v>
       </c>
       <c r="B1" t="str">
-        <v>TWD -2,246,711,546.00</v>
+        <v>TWD 384,680,015.00</v>
       </c>
     </row>
     <row r="2">
@@ -1166,7 +1166,7 @@
         <v>現金</v>
       </c>
       <c r="B2" t="str">
-        <v>TWD 3,471,957,831.00</v>
+        <v>TWD 1,873,136,365.00</v>
       </c>
     </row>
   </sheetData>
